--- a/etf_holdings/2026-10-06_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-06_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1305,7 +1305,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1315,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>222000</v>
+        <v>8000000</v>
       </c>
       <c r="K15" t="n">
-        <v>111000</v>
+        <v>8500000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-111,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-05_00982A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,60 +1378,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3715000</v>
+        <v>480000</v>
       </c>
       <c r="K16" t="n">
-        <v>3745000</v>
+        <v>470000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-05_00982A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,105 +1441,123 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3212000</v>
+        <v>10400000</v>
       </c>
       <c r="K17" t="n">
-        <v>3712000</v>
+        <v>9000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>-10,391,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-05_00982A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>871000</v>
+      </c>
       <c r="K18" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>650000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-221,000</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1549,60 +1567,60 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="K19" t="n">
-        <v>11000000</v>
+        <v>5800000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1617,55 +1635,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>38000000</v>
+        <v>200000</v>
       </c>
       <c r="K20" t="n">
-        <v>24000000</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-14,000,000</t>
+          <t>-199,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1680,55 +1698,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.57%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2210000</v>
+        <v>13000000</v>
       </c>
       <c r="K21" t="n">
-        <v>1950000</v>
+        <v>11700000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-260,000</t>
+          <t>-1,300,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1743,55 +1761,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>300000</v>
+        <v>1130000</v>
       </c>
       <c r="K22" t="n">
-        <v>200000</v>
+        <v>1100000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1806,55 +1824,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8460000</v>
+        <v>2700000</v>
       </c>
       <c r="K23" t="n">
-        <v>7800000</v>
+        <v>2600000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-660,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1869,55 +1887,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>570000</v>
+        <v>5200000</v>
       </c>
       <c r="K24" t="n">
-        <v>620000</v>
+        <v>5280000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-05_00403A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,55 +1950,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1000</v>
+        <v>4500000</v>
       </c>
       <c r="K25" t="n">
-        <v>13000</v>
+        <v>4620000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1990,60 +2008,60 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1648000</v>
+        <v>222000</v>
       </c>
       <c r="K26" t="n">
-        <v>2186000</v>
+        <v>111000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>538,000</t>
+          <t>-111,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,55 +2076,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>492000</v>
+        <v>3715000</v>
       </c>
       <c r="K27" t="n">
-        <v>694000</v>
+        <v>3745000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>202,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2121,118 +2139,100 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12.84%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16.01%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+3.17%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>680000</v>
+        <v>3212000</v>
       </c>
       <c r="K28" t="n">
-        <v>920000</v>
+        <v>3712000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.57%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>+3.38%</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>80000</v>
-      </c>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>326000</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>246,000</t>
-        </is>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,55 +2247,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1414000</v>
+        <v>10000000</v>
       </c>
       <c r="K30" t="n">
-        <v>1581000</v>
+        <v>11000000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2305,60 +2305,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>517000</v>
+        <v>38000000</v>
       </c>
       <c r="K31" t="n">
-        <v>598000</v>
+        <v>24000000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>-14,000,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,55 +2373,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>7.66%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>6.57%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3734000</v>
+        <v>2210000</v>
       </c>
       <c r="K32" t="n">
-        <v>1888000</v>
+        <v>1950000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-1,846,000</t>
+          <t>-260,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,60 +2431,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>34000</v>
+        <v>300000</v>
       </c>
       <c r="K33" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>7.53%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>71000</v>
+        <v>8460000</v>
       </c>
       <c r="K34" t="n">
-        <v>99000</v>
+        <v>7800000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>-660,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,48 +2562,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>153000</v>
+        <v>570000</v>
       </c>
       <c r="K35" t="n">
-        <v>268000</v>
+        <v>620000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+          <t>2026-10-05_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2625,43 +2625,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>217000</v>
+        <v>1000</v>
       </c>
       <c r="K36" t="n">
-        <v>357000</v>
+        <v>13000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2688,43 +2688,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>118000</v>
+        <v>1648000</v>
       </c>
       <c r="K37" t="n">
-        <v>189000</v>
+        <v>2186000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>538,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2751,43 +2751,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>177000</v>
+        <v>492000</v>
       </c>
       <c r="K38" t="n">
-        <v>301000</v>
+        <v>694000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>124,000</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2814,43 +2814,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>12.84%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>16.01%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+3.17%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>34000</v>
+        <v>680000</v>
       </c>
       <c r="K39" t="n">
-        <v>56000</v>
+        <v>920000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2877,43 +2877,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+3.38%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>706000</v>
+        <v>80000</v>
       </c>
       <c r="K40" t="n">
-        <v>734000</v>
+        <v>326000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>246,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2935,48 +2935,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5127000</v>
+        <v>1414000</v>
       </c>
       <c r="K41" t="n">
-        <v>3926000</v>
+        <v>1581000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-1,201,000</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3003,43 +3003,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>241000</v>
+        <v>517000</v>
       </c>
       <c r="K42" t="n">
-        <v>336000</v>
+        <v>598000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3061,48 +3061,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>54000</v>
+        <v>3734000</v>
       </c>
       <c r="K43" t="n">
-        <v>97000</v>
+        <v>1888000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>43,000</t>
+          <t>-1,846,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3129,43 +3129,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>18000</v>
+        <v>34000</v>
       </c>
       <c r="K44" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3192,55 +3192,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>76000</v>
+        <v>71000</v>
       </c>
       <c r="K45" t="n">
-        <v>275000</v>
+        <v>99000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>199,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-05_00992A_full_holdings.xlsx</t>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3250,60 +3250,60 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2115000</v>
+        <v>153000</v>
       </c>
       <c r="K46" t="n">
-        <v>1905000</v>
+        <v>268000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-210,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-05_00992A_full_holdings.xlsx</t>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3313,60 +3313,60 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6.76%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5.67%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>344000</v>
+        <v>217000</v>
       </c>
       <c r="K47" t="n">
-        <v>294000</v>
+        <v>357000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-05_00405A_full_holdings.xlsx</t>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3376,114 +3376,807 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6.01%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>213000</v>
+        <v>118000</v>
       </c>
       <c r="K48" t="n">
-        <v>183000</v>
+        <v>189000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-05_00405A_full_holdings.xlsx</t>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+1.33%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>177000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>301000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>124,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2.73%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.98%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>22,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>706000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>734000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>28,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-1.30%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5127000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3926000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-1,201,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>241000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>336000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>新代</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>新代</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>54000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>43,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-05_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>275000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>199,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-05_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>2115000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-210,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-05_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>00405A</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>6.76%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>344000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>294000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-05_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>6.97%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6.01%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>213000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>183000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-05_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>6805</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>富世達</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>3.46%</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>3.23%</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>-0.23%</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J60" t="n">
         <v>371000</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K60" t="n">
         <v>341000</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-30,000</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>2026-10-05_00405A_full_holdings.xlsx</t>
         </is>
